--- a/artfynd/Länken Vitalmen artfynd.xlsx
+++ b/artfynd/Länken Vitalmen artfynd.xlsx
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>16847385</v>
+        <v>89631281</v>
       </c>
       <c r="B3" t="n">
-        <v>78993</v>
+        <v>83307</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,34 +787,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Rammsjöberget, Jmt</t>
+          <t>Horten, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481357</v>
+        <v>481430</v>
       </c>
       <c r="R3" t="n">
-        <v>6918875</v>
+        <v>6918730</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -841,12 +841,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2014-05-21</t>
+          <t>2020-06-01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2014-05-21</t>
+          <t>2020-06-28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -857,37 +857,27 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>barrskog</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>tallåga</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Niina Sallmén, sofia nordin</t>
+          <t>Via Erland Lindblad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>SCA Skog Naturvärdesinventering</t>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>89631281</v>
+        <v>89631330</v>
       </c>
       <c r="B4" t="n">
         <v>83307</v>
@@ -922,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>481430</v>
+        <v>481424</v>
       </c>
       <c r="R4" t="n">
-        <v>6918730</v>
+        <v>6918760</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,10 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>89631330</v>
+        <v>89631227</v>
       </c>
       <c r="B5" t="n">
-        <v>83307</v>
+        <v>79085</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -999,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1023,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>481424</v>
+        <v>481437</v>
       </c>
       <c r="R5" t="n">
-        <v>6918760</v>
+        <v>6918739</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1089,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>89631227</v>
+        <v>16847385</v>
       </c>
       <c r="B6" t="n">
-        <v>79085</v>
+        <v>78993</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1100,34 +1090,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Horten, Jmt</t>
+          <t>Rammsjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>481437</v>
+        <v>481357</v>
       </c>
       <c r="R6" t="n">
-        <v>6918739</v>
+        <v>6918875</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1154,12 +1144,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2020-06-01</t>
+          <t>2014-05-21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2020-06-28</t>
+          <t>2014-05-21</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1170,21 +1160,31 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>barrskog</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>tallåga</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Niina Sallmén</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
+          <t>Niina Sallmén, sofia nordin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+          <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
     </row>
@@ -1998,32 +1998,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>89631347</v>
+        <v>89631070</v>
       </c>
       <c r="B15" t="n">
-        <v>57141</v>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2033,10 +2033,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>481436</v>
+        <v>481393</v>
       </c>
       <c r="R15" t="n">
-        <v>6919011</v>
+        <v>6919342</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2079,11 +2079,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Spillning</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2104,32 +2099,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>89631287</v>
+        <v>89631347</v>
       </c>
       <c r="B16" t="n">
-        <v>79085</v>
+        <v>57141</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2185,6 +2180,11 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2205,32 +2205,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>89631341</v>
+        <v>89631060</v>
       </c>
       <c r="B17" t="n">
-        <v>79085</v>
+        <v>99035</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>219790</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2240,10 +2240,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>481425</v>
+        <v>481328</v>
       </c>
       <c r="R17" t="n">
-        <v>6919048</v>
+        <v>6919358</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2306,10 +2306,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>89631307</v>
+        <v>89631287</v>
       </c>
       <c r="B18" t="n">
-        <v>79917</v>
+        <v>79085</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2317,21 +2317,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2341,10 +2341,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>481445</v>
+        <v>481436</v>
       </c>
       <c r="R18" t="n">
-        <v>6919243</v>
+        <v>6919011</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2407,10 +2407,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>89631351</v>
+        <v>89631341</v>
       </c>
       <c r="B19" t="n">
-        <v>79917</v>
+        <v>79085</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2418,21 +2418,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2442,10 +2442,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>481436</v>
+        <v>481425</v>
       </c>
       <c r="R19" t="n">
-        <v>6919011</v>
+        <v>6919048</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2508,32 +2508,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>89631108</v>
+        <v>89631307</v>
       </c>
       <c r="B20" t="n">
-        <v>80336</v>
+        <v>79917</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6456</v>
+        <v>229821</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2543,10 +2543,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>481132</v>
+        <v>481445</v>
       </c>
       <c r="R20" t="n">
-        <v>6919725</v>
+        <v>6919243</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2609,10 +2609,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>89631095</v>
+        <v>89631351</v>
       </c>
       <c r="B21" t="n">
-        <v>80432</v>
+        <v>79917</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2620,21 +2620,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>229821</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2644,10 +2644,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>481354</v>
+        <v>481436</v>
       </c>
       <c r="R21" t="n">
-        <v>6919617</v>
+        <v>6919011</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2710,10 +2710,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>89631110</v>
+        <v>89631071</v>
       </c>
       <c r="B22" t="n">
-        <v>80432</v>
+        <v>79084</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2721,21 +2721,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2745,10 +2745,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>481326</v>
+        <v>481258</v>
       </c>
       <c r="R22" t="n">
-        <v>6919494</v>
+        <v>6919843</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2811,10 +2811,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>89631070</v>
+        <v>89631058</v>
       </c>
       <c r="B23" t="n">
-        <v>57953</v>
+        <v>79946</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2822,21 +2822,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2846,10 +2846,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>481393</v>
+        <v>481247</v>
       </c>
       <c r="R23" t="n">
-        <v>6919342</v>
+        <v>6919827</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2912,10 +2912,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>89631068</v>
+        <v>89631108</v>
       </c>
       <c r="B24" t="n">
-        <v>57141</v>
+        <v>80336</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2923,21 +2923,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100138</v>
+        <v>6456</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2947,10 +2947,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>481289</v>
+        <v>481132</v>
       </c>
       <c r="R24" t="n">
-        <v>6919634</v>
+        <v>6919725</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3013,32 +3013,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>89631060</v>
+        <v>89631095</v>
       </c>
       <c r="B25" t="n">
-        <v>99035</v>
+        <v>80432</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3048,10 +3048,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>481328</v>
+        <v>481354</v>
       </c>
       <c r="R25" t="n">
-        <v>6919358</v>
+        <v>6919617</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3114,32 +3114,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>89631069</v>
+        <v>89631110</v>
       </c>
       <c r="B26" t="n">
-        <v>99022</v>
+        <v>80432</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220093</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3149,10 +3149,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>481289</v>
+        <v>481326</v>
       </c>
       <c r="R26" t="n">
-        <v>6919626</v>
+        <v>6919494</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3215,32 +3215,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>89631077</v>
+        <v>89631068</v>
       </c>
       <c r="B27" t="n">
-        <v>99118</v>
+        <v>57141</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3250,10 +3250,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>481349</v>
+        <v>481289</v>
       </c>
       <c r="R27" t="n">
-        <v>6919612</v>
+        <v>6919634</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3316,10 +3316,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>89631116</v>
+        <v>89631069</v>
       </c>
       <c r="B28" t="n">
-        <v>99140</v>
+        <v>99022</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3327,21 +3327,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221952</v>
+        <v>220093</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3351,10 +3351,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>481349</v>
+        <v>481289</v>
       </c>
       <c r="R28" t="n">
-        <v>6919612</v>
+        <v>6919626</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3417,32 +3417,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>89631087</v>
+        <v>89631077</v>
       </c>
       <c r="B29" t="n">
-        <v>79085</v>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3452,10 +3452,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>481384</v>
+        <v>481349</v>
       </c>
       <c r="R29" t="n">
-        <v>6919565</v>
+        <v>6919612</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3518,32 +3518,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>89631119</v>
+        <v>89631116</v>
       </c>
       <c r="B30" t="n">
-        <v>79085</v>
+        <v>99140</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>221952</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3553,10 +3553,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>481319</v>
+        <v>481349</v>
       </c>
       <c r="R30" t="n">
-        <v>6919620</v>
+        <v>6919612</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3619,32 +3619,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>89631107</v>
+        <v>89631087</v>
       </c>
       <c r="B31" t="n">
-        <v>97231</v>
+        <v>79085</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2869</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3654,10 +3654,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>481216</v>
+        <v>481384</v>
       </c>
       <c r="R31" t="n">
-        <v>6919962</v>
+        <v>6919565</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3720,10 +3720,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>89631046</v>
+        <v>89631113</v>
       </c>
       <c r="B32" t="n">
-        <v>93197</v>
+        <v>79085</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3731,21 +3731,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3755,10 +3755,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>481177</v>
+        <v>481247</v>
       </c>
       <c r="R32" t="n">
-        <v>6919989</v>
+        <v>6919827</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3821,32 +3821,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>89631047</v>
+        <v>89631118</v>
       </c>
       <c r="B33" t="n">
-        <v>79351</v>
+        <v>79085</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6434</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3856,10 +3856,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>481187</v>
+        <v>481258</v>
       </c>
       <c r="R33" t="n">
-        <v>6919992</v>
+        <v>6919843</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3922,10 +3922,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>89631071</v>
+        <v>89631119</v>
       </c>
       <c r="B34" t="n">
-        <v>79084</v>
+        <v>79085</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3933,21 +3933,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3957,10 +3957,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>481258</v>
+        <v>481319</v>
       </c>
       <c r="R34" t="n">
-        <v>6919843</v>
+        <v>6919620</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4023,32 +4023,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>89631049</v>
+        <v>89631107</v>
       </c>
       <c r="B35" t="n">
-        <v>79946</v>
+        <v>97231</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>2869</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4058,10 +4058,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>481268</v>
+        <v>481216</v>
       </c>
       <c r="R35" t="n">
-        <v>6919923</v>
+        <v>6919962</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4124,10 +4124,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>89631058</v>
+        <v>89631046</v>
       </c>
       <c r="B36" t="n">
-        <v>79946</v>
+        <v>93197</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4135,21 +4135,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4159,10 +4159,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>481247</v>
+        <v>481177</v>
       </c>
       <c r="R36" t="n">
-        <v>6919827</v>
+        <v>6919989</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4225,32 +4225,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>89631052</v>
+        <v>89631047</v>
       </c>
       <c r="B37" t="n">
-        <v>80432</v>
+        <v>79351</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6434</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4260,10 +4260,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>481179</v>
+        <v>481187</v>
       </c>
       <c r="R37" t="n">
-        <v>6920097</v>
+        <v>6919992</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4326,10 +4326,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>89631096</v>
+        <v>89631049</v>
       </c>
       <c r="B38" t="n">
-        <v>80432</v>
+        <v>79946</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4337,21 +4337,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4361,10 +4361,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>481262</v>
+        <v>481268</v>
       </c>
       <c r="R38" t="n">
-        <v>6919941</v>
+        <v>6919923</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4427,32 +4427,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>89631067</v>
+        <v>89631052</v>
       </c>
       <c r="B39" t="n">
-        <v>80461</v>
+        <v>80432</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4462,10 +4462,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>481262</v>
+        <v>481179</v>
       </c>
       <c r="R39" t="n">
-        <v>6919941</v>
+        <v>6920097</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4528,32 +4528,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>89631097</v>
+        <v>89631096</v>
       </c>
       <c r="B40" t="n">
-        <v>80461</v>
+        <v>80432</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4563,10 +4563,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>481179</v>
+        <v>481262</v>
       </c>
       <c r="R40" t="n">
-        <v>6920097</v>
+        <v>6919941</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4629,32 +4629,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>89631039</v>
+        <v>89631067</v>
       </c>
       <c r="B41" t="n">
-        <v>79085</v>
+        <v>80461</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>6462</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4664,10 +4664,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>481266</v>
+        <v>481262</v>
       </c>
       <c r="R41" t="n">
-        <v>6919908</v>
+        <v>6919941</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4730,32 +4730,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>89631113</v>
+        <v>89631097</v>
       </c>
       <c r="B42" t="n">
-        <v>79085</v>
+        <v>80461</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>6462</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4765,10 +4765,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>481247</v>
+        <v>481179</v>
       </c>
       <c r="R42" t="n">
-        <v>6919827</v>
+        <v>6920097</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4831,7 +4831,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>89631118</v>
+        <v>89631039</v>
       </c>
       <c r="B43" t="n">
         <v>79085</v>
@@ -4866,10 +4866,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>481258</v>
+        <v>481266</v>
       </c>
       <c r="R43" t="n">
-        <v>6919843</v>
+        <v>6919908</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5850,32 +5850,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>89631326</v>
+        <v>89631285</v>
       </c>
       <c r="B53" t="n">
-        <v>79351</v>
+        <v>79084</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6434</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5885,10 +5885,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>481819</v>
+        <v>481775</v>
       </c>
       <c r="R53" t="n">
-        <v>6918857</v>
+        <v>6918716</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5951,7 +5951,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>89631226</v>
+        <v>89631299</v>
       </c>
       <c r="B54" t="n">
         <v>79084</v>
@@ -5986,10 +5986,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>481819</v>
+        <v>481779</v>
       </c>
       <c r="R54" t="n">
-        <v>6918857</v>
+        <v>6918774</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6052,7 +6052,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>89631285</v>
+        <v>89631345</v>
       </c>
       <c r="B55" t="n">
         <v>79084</v>
@@ -6087,10 +6087,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>481775</v>
+        <v>481731</v>
       </c>
       <c r="R55" t="n">
-        <v>6918716</v>
+        <v>6918677</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6153,7 +6153,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>89631299</v>
+        <v>96146970</v>
       </c>
       <c r="B56" t="n">
         <v>79084</v>
@@ -6182,19 +6182,20 @@
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Horten, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>481779</v>
+        <v>481888</v>
       </c>
       <c r="R56" t="n">
-        <v>6918774</v>
+        <v>6918581</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6218,12 +6219,22 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2020-06-01</t>
+          <t>2021-09-17</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2020-06-28</t>
+          <t>2021-09-17</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6238,23 +6249,19 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY56" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>89631345</v>
+        <v>110815689</v>
       </c>
       <c r="B57" t="n">
         <v>79084</v>
@@ -6285,14 +6292,14 @@
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Horten, Jmt</t>
+          <t>Vitvattskrogen, Horten, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>481731</v>
+        <v>481932</v>
       </c>
       <c r="R57" t="n">
-        <v>6918677</v>
+        <v>6918718</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6319,12 +6326,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2020-06-01</t>
+          <t>2023-07-13</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2020-06-28</t>
+          <t>2023-07-13</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6335,27 +6342,38 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY57" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>96146970</v>
+        <v>117579472</v>
       </c>
       <c r="B58" t="n">
         <v>79084</v>
@@ -6384,20 +6402,22 @@
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Horten, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>481888</v>
+        <v>481832</v>
       </c>
       <c r="R58" t="n">
-        <v>6918581</v>
+        <v>6918451</v>
       </c>
       <c r="S58" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6421,22 +6441,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2021-09-17</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>14:13</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2021-09-17</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>14:13</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6445,25 +6455,26 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Marielle Löthman , Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>110815689</v>
+        <v>117579633</v>
       </c>
       <c r="B59" t="n">
         <v>79084</v>
@@ -6492,16 +6503,19 @@
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Vitvattskrogen, Horten, Jmt</t>
+          <t>Horten, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>481932</v>
+        <v>481867</v>
       </c>
       <c r="R59" t="n">
-        <v>6918718</v>
+        <v>6918701</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6528,12 +6542,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2023-07-13</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2023-07-13</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6542,43 +6556,29 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Marielle Löthman , Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>117579472</v>
+        <v>89631239</v>
       </c>
       <c r="B60" t="n">
-        <v>79084</v>
+        <v>79946</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6586,37 +6586,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Horten, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>481832</v>
+        <v>481779</v>
       </c>
       <c r="R60" t="n">
-        <v>6918451</v>
+        <v>6918774</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6643,12 +6640,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2020-06-01</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2020-06-28</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6657,29 +6654,32 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Marielle Löthman , Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY60" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>117579633</v>
+        <v>89631310</v>
       </c>
       <c r="B61" t="n">
-        <v>79084</v>
+        <v>79946</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6687,37 +6687,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Horten, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>481867</v>
+        <v>481775</v>
       </c>
       <c r="R61" t="n">
-        <v>6918701</v>
+        <v>6918716</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6744,12 +6741,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2020-06-01</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2020-06-28</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6758,26 +6755,29 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Marielle Löthman , Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY61" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>89631239</v>
+        <v>110815687</v>
       </c>
       <c r="B62" t="n">
         <v>79946</v>
@@ -6808,14 +6808,14 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Horten, Jmt</t>
+          <t>Vitvattskrogen, Horten, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>481779</v>
+        <v>481932</v>
       </c>
       <c r="R62" t="n">
-        <v>6918774</v>
+        <v>6918718</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6842,12 +6842,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2020-06-01</t>
+          <t>2023-07-13</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2020-06-28</t>
+          <t>2023-07-13</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6858,27 +6858,38 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY62" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>89631257</v>
+        <v>117579604</v>
       </c>
       <c r="B63" t="n">
         <v>79946</v>
@@ -6907,16 +6918,19 @@
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Horten, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>481819</v>
+        <v>481662</v>
       </c>
       <c r="R63" t="n">
-        <v>6918857</v>
+        <v>6918518</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6943,12 +6957,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2020-06-01</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2020-06-28</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6957,32 +6971,29 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY63" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Marielle Löthman , Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>89631310</v>
+        <v>117579586</v>
       </c>
       <c r="B64" t="n">
-        <v>79946</v>
+        <v>80432</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6990,34 +7001,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Horten, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>481775</v>
+        <v>481646</v>
       </c>
       <c r="R64" t="n">
-        <v>6918716</v>
+        <v>6918487</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7044,12 +7058,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2020-06-01</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2020-06-28</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7058,67 +7072,72 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY64" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Marielle Löthman , Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>110815687</v>
+        <v>117579560</v>
       </c>
       <c r="B65" t="n">
-        <v>79946</v>
+        <v>57141</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Vitvattskrogen, Horten, Jmt</t>
+          <t>Horten, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>481932</v>
+        <v>481705</v>
       </c>
       <c r="R65" t="n">
-        <v>6918718</v>
+        <v>6918516</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7145,12 +7164,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2023-07-13</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2023-07-13</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7161,79 +7180,61 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ65" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK65" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Marielle Löthman , Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>117579604</v>
+        <v>89631298</v>
       </c>
       <c r="B66" t="n">
-        <v>79946</v>
+        <v>99022</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6453</v>
+        <v>220093</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Horten, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>481662</v>
+        <v>481502</v>
       </c>
       <c r="R66" t="n">
-        <v>6918518</v>
+        <v>6918624</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7260,12 +7261,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2020-06-01</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2020-06-28</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7274,29 +7275,32 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Marielle Löthman , Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY66" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>89631343</v>
+        <v>89631263</v>
       </c>
       <c r="B67" t="n">
-        <v>80336</v>
+        <v>99140</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7304,21 +7308,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6456</v>
+        <v>221952</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7328,10 +7332,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>481839</v>
+        <v>481470</v>
       </c>
       <c r="R67" t="n">
-        <v>6918844</v>
+        <v>6918667</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7394,10 +7398,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>117579586</v>
+        <v>89631231</v>
       </c>
       <c r="B68" t="n">
-        <v>80432</v>
+        <v>79085</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7405,37 +7409,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Horten, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>481646</v>
+        <v>481779</v>
       </c>
       <c r="R68" t="n">
-        <v>6918487</v>
+        <v>6918774</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7462,12 +7463,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2020-06-01</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2020-06-28</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7476,29 +7477,32 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Marielle Löthman , Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY68" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>89631268</v>
+        <v>89631274</v>
       </c>
       <c r="B69" t="n">
-        <v>78334</v>
+        <v>79085</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7506,21 +7510,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7530,10 +7534,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>481819</v>
+        <v>481775</v>
       </c>
       <c r="R69" t="n">
-        <v>6918857</v>
+        <v>6918716</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7596,53 +7600,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>117579560</v>
+        <v>89631306</v>
       </c>
       <c r="B70" t="n">
-        <v>57141</v>
+        <v>79085</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Horten, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>481705</v>
+        <v>481743</v>
       </c>
       <c r="R70" t="n">
-        <v>6918516</v>
+        <v>6918689</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7669,12 +7665,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2020-06-01</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2020-06-28</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7689,57 +7685,61 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Marielle Löthman , Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY70" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>89631298</v>
+        <v>110815688</v>
       </c>
       <c r="B71" t="n">
-        <v>99022</v>
+        <v>79085</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220093</v>
+        <v>228912</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Horten, Jmt</t>
+          <t>Vitvattskrogen, Horten, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>481502</v>
+        <v>481932</v>
       </c>
       <c r="R71" t="n">
-        <v>6918624</v>
+        <v>6918718</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7766,12 +7766,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2020-06-01</t>
+          <t>2023-07-13</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2020-06-28</t>
+          <t>2023-07-13</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7782,65 +7782,79 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY71" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>89631263</v>
+        <v>117579497</v>
       </c>
       <c r="B72" t="n">
-        <v>99140</v>
+        <v>79085</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>221952</v>
+        <v>228912</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Horten, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>481470</v>
+        <v>481832</v>
       </c>
       <c r="R72" t="n">
-        <v>6918667</v>
+        <v>6918451</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7867,12 +7881,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2020-06-01</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2020-06-28</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7881,29 +7895,26 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY72" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Marielle Löthman , Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>89631231</v>
+        <v>117579529</v>
       </c>
       <c r="B73" t="n">
         <v>79085</v>
@@ -7932,16 +7943,19 @@
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Horten, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>481779</v>
+        <v>481596</v>
       </c>
       <c r="R73" t="n">
-        <v>6918774</v>
+        <v>6918571</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7968,12 +7982,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2020-06-01</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2020-06-28</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7982,29 +7996,26 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY73" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Marielle Löthman , Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>89631274</v>
+        <v>117579616</v>
       </c>
       <c r="B74" t="n">
         <v>79085</v>
@@ -8033,16 +8044,19 @@
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Horten, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>481775</v>
+        <v>481826</v>
       </c>
       <c r="R74" t="n">
-        <v>6918716</v>
+        <v>6918644</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8069,12 +8083,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2020-06-01</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2020-06-28</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8083,29 +8097,26 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY74" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Marielle Löthman , Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>89631306</v>
+        <v>117579629</v>
       </c>
       <c r="B75" t="n">
         <v>79085</v>
@@ -8134,16 +8145,19 @@
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Horten, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>481743</v>
+        <v>481945</v>
       </c>
       <c r="R75" t="n">
-        <v>6918689</v>
+        <v>6918731</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8170,12 +8184,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2020-06-01</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2020-06-28</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8184,32 +8198,29 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY75" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Marielle Löthman , Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>89631327</v>
+        <v>89631328</v>
       </c>
       <c r="B76" t="n">
-        <v>79085</v>
+        <v>90932</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8217,34 +8228,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>228912</v>
+        <v>1962</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Horten, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>481818</v>
+        <v>481461</v>
       </c>
       <c r="R76" t="n">
-        <v>6918833</v>
+        <v>6919254</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8283,8 +8297,9 @@
         <v>0</v>
       </c>
       <c r="AE76" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8307,32 +8322,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>89631335</v>
+        <v>89631326</v>
       </c>
       <c r="B77" t="n">
-        <v>79085</v>
+        <v>79351</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>228912</v>
+        <v>6434</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8342,10 +8357,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>481838</v>
+        <v>481819</v>
       </c>
       <c r="R77" t="n">
-        <v>6918839</v>
+        <v>6918857</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8408,10 +8423,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>89631349</v>
+        <v>89631228</v>
       </c>
       <c r="B78" t="n">
-        <v>79085</v>
+        <v>78730</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8419,21 +8434,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8443,10 +8458,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>481819</v>
+        <v>481486</v>
       </c>
       <c r="R78" t="n">
-        <v>6918857</v>
+        <v>6919035</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8509,10 +8524,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>110815688</v>
+        <v>89631226</v>
       </c>
       <c r="B79" t="n">
-        <v>79085</v>
+        <v>79084</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8520,34 +8535,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Vitvattskrogen, Horten, Jmt</t>
+          <t>Horten, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>481932</v>
+        <v>481819</v>
       </c>
       <c r="R79" t="n">
-        <v>6918718</v>
+        <v>6918857</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8574,12 +8589,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2023-07-13</t>
+          <t>2020-06-01</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2023-07-13</t>
+          <t>2020-06-28</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8590,41 +8605,30 @@
       </c>
       <c r="AG79" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ79" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK79" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO79" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
-        </is>
-      </c>
-      <c r="AY79" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>117579497</v>
+        <v>89631241</v>
       </c>
       <c r="B80" t="n">
-        <v>79085</v>
+        <v>79946</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8632,37 +8636,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Horten, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>481832</v>
+        <v>481486</v>
       </c>
       <c r="R80" t="n">
-        <v>6918451</v>
+        <v>6919035</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8689,12 +8690,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2020-06-01</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2020-06-28</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8703,29 +8704,32 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Marielle Löthman , Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY80" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>117579529</v>
+        <v>89631257</v>
       </c>
       <c r="B81" t="n">
-        <v>79085</v>
+        <v>79946</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8733,37 +8737,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Horten, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>481596</v>
+        <v>481819</v>
       </c>
       <c r="R81" t="n">
-        <v>6918571</v>
+        <v>6918857</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8790,12 +8791,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2020-06-01</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2020-06-28</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8804,29 +8805,32 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Marielle Löthman , Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY81" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>117579616</v>
+        <v>89631276</v>
       </c>
       <c r="B82" t="n">
-        <v>79085</v>
+        <v>79946</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8834,37 +8838,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Horten, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>481826</v>
+        <v>481450</v>
       </c>
       <c r="R82" t="n">
-        <v>6918644</v>
+        <v>6919195</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8891,12 +8892,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2020-06-01</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2020-06-28</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8905,67 +8906,67 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Marielle Löthman , Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY82" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>117579629</v>
+        <v>89631343</v>
       </c>
       <c r="B83" t="n">
-        <v>79085</v>
+        <v>80336</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>228912</v>
+        <v>6456</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Horten, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>481945</v>
+        <v>481839</v>
       </c>
       <c r="R83" t="n">
-        <v>6918731</v>
+        <v>6918844</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8992,12 +8993,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2020-06-01</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2020-06-28</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9006,29 +9007,32 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Marielle Löthman , Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY83" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>89631236</v>
+        <v>89631268</v>
       </c>
       <c r="B84" t="n">
-        <v>79917</v>
+        <v>78334</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9036,21 +9040,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>229821</v>
+        <v>6487</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9126,10 +9130,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>89631328</v>
+        <v>89631318</v>
       </c>
       <c r="B85" t="n">
-        <v>90932</v>
+        <v>78334</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9137,37 +9141,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1962</v>
+        <v>6487</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Horten, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>481461</v>
+        <v>481486</v>
       </c>
       <c r="R85" t="n">
-        <v>6919254</v>
+        <v>6919035</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9206,9 +9207,8 @@
         <v>0</v>
       </c>
       <c r="AE85" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF85" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -9231,10 +9231,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>89631228</v>
+        <v>89631102</v>
       </c>
       <c r="B86" t="n">
-        <v>78730</v>
+        <v>57953</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9242,21 +9242,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6437</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9266,10 +9266,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>481486</v>
+        <v>481554</v>
       </c>
       <c r="R86" t="n">
-        <v>6919035</v>
+        <v>6919336</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9332,32 +9332,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>89631241</v>
+        <v>89631320</v>
       </c>
       <c r="B87" t="n">
-        <v>79946</v>
+        <v>99118</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9367,10 +9367,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>481486</v>
+        <v>481477</v>
       </c>
       <c r="R87" t="n">
-        <v>6919035</v>
+        <v>6919155</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9433,10 +9433,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>89631276</v>
+        <v>89631313</v>
       </c>
       <c r="B88" t="n">
-        <v>79946</v>
+        <v>79085</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9444,21 +9444,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9468,10 +9468,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>481450</v>
+        <v>481486</v>
       </c>
       <c r="R88" t="n">
-        <v>6919195</v>
+        <v>6919030</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9534,10 +9534,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>89631318</v>
+        <v>89631327</v>
       </c>
       <c r="B89" t="n">
-        <v>78334</v>
+        <v>79085</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9545,21 +9545,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9569,10 +9569,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>481486</v>
+        <v>481818</v>
       </c>
       <c r="R89" t="n">
-        <v>6919035</v>
+        <v>6918833</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9635,10 +9635,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>89631102</v>
+        <v>89631335</v>
       </c>
       <c r="B90" t="n">
-        <v>57953</v>
+        <v>79085</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9646,21 +9646,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>481554</v>
+        <v>481838</v>
       </c>
       <c r="R90" t="n">
-        <v>6919336</v>
+        <v>6918839</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9736,32 +9736,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>89631320</v>
+        <v>89631349</v>
       </c>
       <c r="B91" t="n">
-        <v>99118</v>
+        <v>79085</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9771,10 +9771,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>481477</v>
+        <v>481819</v>
       </c>
       <c r="R91" t="n">
-        <v>6919155</v>
+        <v>6918857</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9837,10 +9837,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>89631313</v>
+        <v>89631236</v>
       </c>
       <c r="B92" t="n">
-        <v>79085</v>
+        <v>79917</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9848,21 +9848,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9872,10 +9872,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>481486</v>
+        <v>481819</v>
       </c>
       <c r="R92" t="n">
-        <v>6919030</v>
+        <v>6918857</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10261,10 +10261,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>89631243</v>
+        <v>89631233</v>
       </c>
       <c r="B96" t="n">
-        <v>78730</v>
+        <v>93197</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10272,21 +10272,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10296,10 +10296,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>481522</v>
+        <v>481737</v>
       </c>
       <c r="R96" t="n">
-        <v>6919603</v>
+        <v>6919898</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10362,7 +10362,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>89631258</v>
+        <v>89631243</v>
       </c>
       <c r="B97" t="n">
         <v>78730</v>
@@ -10397,10 +10397,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>481489</v>
+        <v>481522</v>
       </c>
       <c r="R97" t="n">
-        <v>6919442</v>
+        <v>6919603</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10463,7 +10463,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>89631267</v>
+        <v>89631258</v>
       </c>
       <c r="B98" t="n">
         <v>78730</v>
@@ -10498,10 +10498,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>481488</v>
+        <v>481489</v>
       </c>
       <c r="R98" t="n">
-        <v>6919484</v>
+        <v>6919442</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10564,10 +10564,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>89631253</v>
+        <v>89631267</v>
       </c>
       <c r="B99" t="n">
-        <v>79084</v>
+        <v>78730</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10575,21 +10575,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10602,7 +10602,7 @@
         <v>481488</v>
       </c>
       <c r="R99" t="n">
-        <v>6919486</v>
+        <v>6919484</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10665,7 +10665,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>89631259</v>
+        <v>89631253</v>
       </c>
       <c r="B100" t="n">
         <v>79084</v>
@@ -10700,10 +10700,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>481612</v>
+        <v>481488</v>
       </c>
       <c r="R100" t="n">
-        <v>6919615</v>
+        <v>6919486</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10766,7 +10766,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>89631278</v>
+        <v>89631259</v>
       </c>
       <c r="B101" t="n">
         <v>79084</v>
@@ -10801,10 +10801,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>481797</v>
+        <v>481612</v>
       </c>
       <c r="R101" t="n">
-        <v>6919649</v>
+        <v>6919615</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10867,7 +10867,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>89631288</v>
+        <v>89631278</v>
       </c>
       <c r="B102" t="n">
         <v>79084</v>
@@ -10902,10 +10902,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>481551</v>
+        <v>481797</v>
       </c>
       <c r="R102" t="n">
-        <v>6919564</v>
+        <v>6919649</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10968,7 +10968,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>89631339</v>
+        <v>89631288</v>
       </c>
       <c r="B103" t="n">
         <v>79084</v>
@@ -11003,10 +11003,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>481497</v>
+        <v>481551</v>
       </c>
       <c r="R103" t="n">
-        <v>6919430</v>
+        <v>6919564</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11069,10 +11069,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>89631249</v>
+        <v>89631339</v>
       </c>
       <c r="B104" t="n">
-        <v>79946</v>
+        <v>79084</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11080,21 +11080,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11104,10 +11104,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>481551</v>
+        <v>481497</v>
       </c>
       <c r="R104" t="n">
-        <v>6919564</v>
+        <v>6919430</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11170,7 +11170,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>89631255</v>
+        <v>89631249</v>
       </c>
       <c r="B105" t="n">
         <v>79946</v>
@@ -11205,10 +11205,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>481797</v>
+        <v>481551</v>
       </c>
       <c r="R105" t="n">
-        <v>6919649</v>
+        <v>6919564</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11271,7 +11271,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>89631283</v>
+        <v>89631255</v>
       </c>
       <c r="B106" t="n">
         <v>79946</v>
@@ -11306,10 +11306,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>481612</v>
+        <v>481797</v>
       </c>
       <c r="R106" t="n">
-        <v>6919615</v>
+        <v>6919649</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11372,32 +11372,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>89631237</v>
+        <v>89631283</v>
       </c>
       <c r="B107" t="n">
-        <v>80336</v>
+        <v>79946</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6456</v>
+        <v>6453</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11407,10 +11407,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>481573</v>
+        <v>481612</v>
       </c>
       <c r="R107" t="n">
-        <v>6919633</v>
+        <v>6919615</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11473,32 +11473,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>89631240</v>
+        <v>89631237</v>
       </c>
       <c r="B108" t="n">
-        <v>80432</v>
+        <v>80336</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11508,10 +11508,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>481810</v>
+        <v>481573</v>
       </c>
       <c r="R108" t="n">
-        <v>6919662</v>
+        <v>6919633</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11574,7 +11574,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>89631244</v>
+        <v>89631085</v>
       </c>
       <c r="B109" t="n">
         <v>80432</v>
@@ -11609,10 +11609,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>481811</v>
+        <v>481600</v>
       </c>
       <c r="R109" t="n">
-        <v>6919716</v>
+        <v>6919851</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11675,7 +11675,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>89631302</v>
+        <v>89631240</v>
       </c>
       <c r="B110" t="n">
         <v>80432</v>
@@ -11710,10 +11710,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>481795</v>
+        <v>481810</v>
       </c>
       <c r="R110" t="n">
-        <v>6919677</v>
+        <v>6919662</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11776,32 +11776,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>89631232</v>
+        <v>89631244</v>
       </c>
       <c r="B111" t="n">
-        <v>80461</v>
+        <v>80432</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11811,10 +11811,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>481525</v>
+        <v>481811</v>
       </c>
       <c r="R111" t="n">
-        <v>6919599</v>
+        <v>6919716</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11877,32 +11877,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>89631235</v>
+        <v>89631302</v>
       </c>
       <c r="B112" t="n">
-        <v>80461</v>
+        <v>80432</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11912,10 +11912,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>481810</v>
+        <v>481795</v>
       </c>
       <c r="R112" t="n">
-        <v>6919662</v>
+        <v>6919677</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11978,7 +11978,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>89631270</v>
+        <v>89631232</v>
       </c>
       <c r="B113" t="n">
         <v>80461</v>
@@ -12013,10 +12013,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>481795</v>
+        <v>481525</v>
       </c>
       <c r="R113" t="n">
-        <v>6919677</v>
+        <v>6919599</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12079,10 +12079,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>89631271</v>
+        <v>89631235</v>
       </c>
       <c r="B114" t="n">
-        <v>80467</v>
+        <v>80461</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12090,21 +12090,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12114,10 +12114,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>481525</v>
+        <v>481810</v>
       </c>
       <c r="R114" t="n">
-        <v>6919600</v>
+        <v>6919662</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12180,10 +12180,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>89631293</v>
+        <v>89631270</v>
       </c>
       <c r="B115" t="n">
-        <v>80467</v>
+        <v>80461</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12191,21 +12191,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12215,10 +12215,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>481810</v>
+        <v>481795</v>
       </c>
       <c r="R115" t="n">
-        <v>6919662</v>
+        <v>6919677</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12281,7 +12281,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>89631300</v>
+        <v>89631271</v>
       </c>
       <c r="B116" t="n">
         <v>80467</v>
@@ -12316,10 +12316,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>481795</v>
+        <v>481525</v>
       </c>
       <c r="R116" t="n">
-        <v>6919677</v>
+        <v>6919600</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12382,10 +12382,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>89631074</v>
+        <v>89631293</v>
       </c>
       <c r="B117" t="n">
-        <v>99035</v>
+        <v>80467</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12393,21 +12393,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>219790</v>
+        <v>6463</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12417,10 +12417,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>481511</v>
+        <v>481810</v>
       </c>
       <c r="R117" t="n">
-        <v>6919511</v>
+        <v>6919662</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12483,10 +12483,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>89631279</v>
+        <v>89631300</v>
       </c>
       <c r="B118" t="n">
-        <v>99035</v>
+        <v>80467</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12494,21 +12494,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>219790</v>
+        <v>6463</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12518,10 +12518,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>481569</v>
+        <v>481795</v>
       </c>
       <c r="R118" t="n">
-        <v>6919654</v>
+        <v>6919677</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12584,7 +12584,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>89631305</v>
+        <v>89631074</v>
       </c>
       <c r="B119" t="n">
         <v>99035</v>
@@ -12619,10 +12619,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>481542</v>
+        <v>481511</v>
       </c>
       <c r="R119" t="n">
-        <v>6919572</v>
+        <v>6919511</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12685,10 +12685,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>89631064</v>
+        <v>89631279</v>
       </c>
       <c r="B120" t="n">
-        <v>99153</v>
+        <v>99035</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12696,21 +12696,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>219874</v>
+        <v>219790</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12720,10 +12720,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>481508</v>
+        <v>481569</v>
       </c>
       <c r="R120" t="n">
-        <v>6919512</v>
+        <v>6919654</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12786,10 +12786,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>89631099</v>
+        <v>89631305</v>
       </c>
       <c r="B121" t="n">
-        <v>99153</v>
+        <v>99035</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12797,21 +12797,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>219874</v>
+        <v>219790</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12821,10 +12821,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>481510</v>
+        <v>481542</v>
       </c>
       <c r="R121" t="n">
-        <v>6919533</v>
+        <v>6919572</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12887,7 +12887,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>89631260</v>
+        <v>89631064</v>
       </c>
       <c r="B122" t="n">
         <v>99153</v>
@@ -12922,10 +12922,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>481579</v>
+        <v>481508</v>
       </c>
       <c r="R122" t="n">
-        <v>6919641</v>
+        <v>6919512</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12988,7 +12988,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>89631277</v>
+        <v>89631099</v>
       </c>
       <c r="B123" t="n">
         <v>99153</v>
@@ -13023,10 +13023,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>481528</v>
+        <v>481510</v>
       </c>
       <c r="R123" t="n">
-        <v>6919532</v>
+        <v>6919533</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13089,32 +13089,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>89631238</v>
+        <v>89631260</v>
       </c>
       <c r="B124" t="n">
-        <v>99118</v>
+        <v>99153</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13124,10 +13124,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>481529</v>
+        <v>481579</v>
       </c>
       <c r="R124" t="n">
-        <v>6919596</v>
+        <v>6919641</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13190,32 +13190,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>89631250</v>
+        <v>89631277</v>
       </c>
       <c r="B125" t="n">
-        <v>99118</v>
+        <v>99153</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13225,10 +13225,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>481516</v>
+        <v>481528</v>
       </c>
       <c r="R125" t="n">
-        <v>6919544</v>
+        <v>6919532</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13291,7 +13291,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>89631254</v>
+        <v>89631238</v>
       </c>
       <c r="B126" t="n">
         <v>99118</v>
@@ -13326,10 +13326,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>481486</v>
+        <v>481529</v>
       </c>
       <c r="R126" t="n">
-        <v>6919517</v>
+        <v>6919596</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13392,7 +13392,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>89631280</v>
+        <v>89631250</v>
       </c>
       <c r="B127" t="n">
         <v>99118</v>
@@ -13427,10 +13427,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>481551</v>
+        <v>481516</v>
       </c>
       <c r="R127" t="n">
-        <v>6919568</v>
+        <v>6919544</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13493,7 +13493,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>89631321</v>
+        <v>89631254</v>
       </c>
       <c r="B128" t="n">
         <v>99118</v>
@@ -13528,10 +13528,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>481551</v>
+        <v>481486</v>
       </c>
       <c r="R128" t="n">
-        <v>6919565</v>
+        <v>6919517</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13594,7 +13594,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>89631332</v>
+        <v>89631280</v>
       </c>
       <c r="B129" t="n">
         <v>99118</v>
@@ -13629,10 +13629,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>481549</v>
+        <v>481551</v>
       </c>
       <c r="R129" t="n">
-        <v>6919572</v>
+        <v>6919568</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13695,7 +13695,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>89631337</v>
+        <v>89631321</v>
       </c>
       <c r="B130" t="n">
         <v>99118</v>
@@ -13730,10 +13730,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>481536</v>
+        <v>481551</v>
       </c>
       <c r="R130" t="n">
-        <v>6919529</v>
+        <v>6919565</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13796,7 +13796,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>96561033</v>
+        <v>89631332</v>
       </c>
       <c r="B131" t="n">
         <v>99118</v>
@@ -13827,17 +13827,17 @@
       <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Rammsjöberget /2 km O/, Jmt</t>
+          <t>Horten, Jmt</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>481508</v>
+        <v>481549</v>
       </c>
       <c r="R131" t="n">
-        <v>6919563</v>
+        <v>6919572</v>
       </c>
       <c r="S131" t="n">
-        <v>125</v>
+        <v>10</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -13859,11 +13859,6 @@
           <t>Rätan</t>
         </is>
       </c>
-      <c r="X131" t="inlineStr">
-        <is>
-          <t>Z-Ber-1673</t>
-        </is>
-      </c>
       <c r="Y131" t="inlineStr">
         <is>
           <t>2020-06-01</t>
@@ -13872,11 +13867,6 @@
       <c r="AA131" t="inlineStr">
         <is>
           <t>2020-06-28</t>
-        </is>
-      </c>
-      <c r="AC131" t="inlineStr">
-        <is>
-          <t>Noterad på lokal Horten vid åtta koordinat: O1439725, N6922245 (±10m), O1439861, N6922148 (±10m), O1439891, N6922174 (±10m), O1439905, N6922227 (±10m), O1439911, N6922159 (±10m), O1439924, N6922202 (±10m), O1439927, N6922195 (±10m), O1439927, N6922198 (±10m) RT90 2.5 gon. Observatör ej angiven. Summerat till floraväkteriet.</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -13891,48 +13881,48 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Lars-Åke Bäckström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Via Lars-Åke Bäckström</t>
+          <t>Via Erland Lindblad</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
         <is>
-          <t>Floraväkteri Sverige</t>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>89631229</v>
+        <v>89631337</v>
       </c>
       <c r="B132" t="n">
-        <v>99140</v>
+        <v>99118</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13942,10 +13932,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>481473</v>
+        <v>481536</v>
       </c>
       <c r="R132" t="n">
-        <v>6919515</v>
+        <v>6919529</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14008,48 +13998,48 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>89631256</v>
+        <v>96561033</v>
       </c>
       <c r="B133" t="n">
-        <v>99140</v>
+        <v>99118</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Horten, Jmt</t>
+          <t>Rammsjöberget /2 km O/, Jmt</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>481521</v>
+        <v>481508</v>
       </c>
       <c r="R133" t="n">
-        <v>6919548</v>
+        <v>6919563</v>
       </c>
       <c r="S133" t="n">
-        <v>10</v>
+        <v>125</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -14071,6 +14061,11 @@
           <t>Rätan</t>
         </is>
       </c>
+      <c r="X133" t="inlineStr">
+        <is>
+          <t>Z-Ber-1673</t>
+        </is>
+      </c>
       <c r="Y133" t="inlineStr">
         <is>
           <t>2020-06-01</t>
@@ -14079,6 +14074,11 @@
       <c r="AA133" t="inlineStr">
         <is>
           <t>2020-06-28</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>Noterad på lokal Horten vid åtta koordinat: O1439725, N6922245 (±10m), O1439861, N6922148 (±10m), O1439891, N6922174 (±10m), O1439905, N6922227 (±10m), O1439911, N6922159 (±10m), O1439924, N6922202 (±10m), O1439927, N6922195 (±10m), O1439927, N6922198 (±10m) RT90 2.5 gon. Observatör ej angiven. Summerat till floraväkteriet.</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14093,23 +14093,23 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars-Åke Bäckström</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
+          <t>Via Lars-Åke Bäckström</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr">
         <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+          <t>Floraväkteri Sverige</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>89631350</v>
+        <v>89631229</v>
       </c>
       <c r="B134" t="n">
         <v>99140</v>
@@ -14144,10 +14144,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>481541</v>
+        <v>481473</v>
       </c>
       <c r="R134" t="n">
-        <v>6919532</v>
+        <v>6919515</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14210,32 +14210,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>89631117</v>
+        <v>89631256</v>
       </c>
       <c r="B135" t="n">
-        <v>79085</v>
+        <v>99140</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>228912</v>
+        <v>221952</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14245,10 +14245,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>481531</v>
+        <v>481521</v>
       </c>
       <c r="R135" t="n">
-        <v>6919665</v>
+        <v>6919548</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14311,32 +14311,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>89631290</v>
+        <v>89631350</v>
       </c>
       <c r="B136" t="n">
-        <v>79085</v>
+        <v>99140</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>228912</v>
+        <v>221952</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14346,10 +14346,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>481612</v>
+        <v>481541</v>
       </c>
       <c r="R136" t="n">
-        <v>6919615</v>
+        <v>6919532</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14412,7 +14412,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>89631304</v>
+        <v>89631117</v>
       </c>
       <c r="B137" t="n">
         <v>79085</v>
@@ -14447,10 +14447,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>481486</v>
+        <v>481531</v>
       </c>
       <c r="R137" t="n">
-        <v>6919485</v>
+        <v>6919665</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14513,7 +14513,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>89631309</v>
+        <v>89631290</v>
       </c>
       <c r="B138" t="n">
         <v>79085</v>
@@ -14548,10 +14548,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>481791</v>
+        <v>481612</v>
       </c>
       <c r="R138" t="n">
-        <v>6919644</v>
+        <v>6919615</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14614,7 +14614,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>89631322</v>
+        <v>89631304</v>
       </c>
       <c r="B139" t="n">
         <v>79085</v>
@@ -14649,10 +14649,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>481496</v>
+        <v>481486</v>
       </c>
       <c r="R139" t="n">
-        <v>6919427</v>
+        <v>6919485</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14715,7 +14715,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>89631331</v>
+        <v>89631309</v>
       </c>
       <c r="B140" t="n">
         <v>79085</v>
@@ -14750,10 +14750,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>481811</v>
+        <v>481791</v>
       </c>
       <c r="R140" t="n">
-        <v>6919718</v>
+        <v>6919644</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14816,10 +14816,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>89631308</v>
+        <v>89631322</v>
       </c>
       <c r="B141" t="n">
-        <v>79917</v>
+        <v>79085</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14827,27 +14827,24 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
-      <c r="J141" t="inlineStr"/>
-      <c r="K141" t="inlineStr"/>
-      <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
           <t>Horten, Jmt</t>
@@ -14857,7 +14854,7 @@
         <v>481496</v>
       </c>
       <c r="R141" t="n">
-        <v>6919431</v>
+        <v>6919427</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14898,7 +14895,6 @@
       <c r="AE141" t="b">
         <v>0</v>
       </c>
-      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
@@ -14921,10 +14917,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>89631233</v>
+        <v>89631331</v>
       </c>
       <c r="B142" t="n">
-        <v>93197</v>
+        <v>79085</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14932,21 +14928,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14956,10 +14952,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>481737</v>
+        <v>481811</v>
       </c>
       <c r="R142" t="n">
-        <v>6919898</v>
+        <v>6919718</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15022,45 +15018,48 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>89631078</v>
+        <v>89631308</v>
       </c>
       <c r="B143" t="n">
-        <v>79327</v>
+        <v>79917</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
+      <c r="J143" t="inlineStr"/>
+      <c r="K143" t="inlineStr"/>
+      <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
           <t>Horten, Jmt</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>481617</v>
+        <v>481496</v>
       </c>
       <c r="R143" t="n">
-        <v>6919941</v>
+        <v>6919431</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15101,6 +15100,7 @@
       <c r="AE143" t="b">
         <v>0</v>
       </c>
+      <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>0</v>
       </c>
@@ -15123,32 +15123,32 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>89631120</v>
+        <v>89631078</v>
       </c>
       <c r="B144" t="n">
-        <v>80336</v>
+        <v>79327</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15158,10 +15158,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>481481</v>
+        <v>481617</v>
       </c>
       <c r="R144" t="n">
-        <v>6920010</v>
+        <v>6919941</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15224,32 +15224,32 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>89631040</v>
+        <v>89631120</v>
       </c>
       <c r="B145" t="n">
-        <v>80432</v>
+        <v>80336</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15259,10 +15259,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>481489</v>
+        <v>481481</v>
       </c>
       <c r="R145" t="n">
-        <v>6920059</v>
+        <v>6920010</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15325,7 +15325,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>89631041</v>
+        <v>89631040</v>
       </c>
       <c r="B146" t="n">
         <v>80432</v>
@@ -15360,10 +15360,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>481464</v>
+        <v>481489</v>
       </c>
       <c r="R146" t="n">
-        <v>6920049</v>
+        <v>6920059</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15426,7 +15426,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>89631043</v>
+        <v>89631041</v>
       </c>
       <c r="B147" t="n">
         <v>80432</v>
@@ -15461,10 +15461,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>481483</v>
+        <v>481464</v>
       </c>
       <c r="R147" t="n">
-        <v>6920088</v>
+        <v>6920049</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15527,7 +15527,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>89631051</v>
+        <v>89631043</v>
       </c>
       <c r="B148" t="n">
         <v>80432</v>
@@ -15562,10 +15562,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>481478</v>
+        <v>481483</v>
       </c>
       <c r="R148" t="n">
-        <v>6920005</v>
+        <v>6920088</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15628,7 +15628,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>89631053</v>
+        <v>89631051</v>
       </c>
       <c r="B149" t="n">
         <v>80432</v>
@@ -15663,10 +15663,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>481487</v>
+        <v>481478</v>
       </c>
       <c r="R149" t="n">
-        <v>6920101</v>
+        <v>6920005</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15729,7 +15729,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>89631057</v>
+        <v>89631053</v>
       </c>
       <c r="B150" t="n">
         <v>80432</v>
@@ -15764,10 +15764,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>481467</v>
+        <v>481487</v>
       </c>
       <c r="R150" t="n">
-        <v>6920024</v>
+        <v>6920101</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15830,7 +15830,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>89631062</v>
+        <v>89631057</v>
       </c>
       <c r="B151" t="n">
         <v>80432</v>
@@ -15865,10 +15865,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>481481</v>
+        <v>481467</v>
       </c>
       <c r="R151" t="n">
-        <v>6920016</v>
+        <v>6920024</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15931,7 +15931,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>89631065</v>
+        <v>89631062</v>
       </c>
       <c r="B152" t="n">
         <v>80432</v>
@@ -15966,10 +15966,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>481605</v>
+        <v>481481</v>
       </c>
       <c r="R152" t="n">
-        <v>6919914</v>
+        <v>6920016</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16032,7 +16032,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>89631066</v>
+        <v>89631065</v>
       </c>
       <c r="B153" t="n">
         <v>80432</v>
@@ -16067,10 +16067,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>481607</v>
+        <v>481605</v>
       </c>
       <c r="R153" t="n">
-        <v>6920005</v>
+        <v>6919914</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16133,7 +16133,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>89631073</v>
+        <v>89631066</v>
       </c>
       <c r="B154" t="n">
         <v>80432</v>
@@ -16168,10 +16168,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>481627</v>
+        <v>481607</v>
       </c>
       <c r="R154" t="n">
-        <v>6919976</v>
+        <v>6920005</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16234,7 +16234,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>89631079</v>
+        <v>89631073</v>
       </c>
       <c r="B155" t="n">
         <v>80432</v>
@@ -16269,10 +16269,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>481502</v>
+        <v>481627</v>
       </c>
       <c r="R155" t="n">
-        <v>6920009</v>
+        <v>6919976</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16335,7 +16335,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>89631080</v>
+        <v>89631079</v>
       </c>
       <c r="B156" t="n">
         <v>80432</v>
@@ -16370,10 +16370,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>481591</v>
+        <v>481502</v>
       </c>
       <c r="R156" t="n">
-        <v>6920117</v>
+        <v>6920009</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16436,7 +16436,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>89631082</v>
+        <v>89631080</v>
       </c>
       <c r="B157" t="n">
         <v>80432</v>
@@ -16471,10 +16471,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>481498</v>
+        <v>481591</v>
       </c>
       <c r="R157" t="n">
-        <v>6920013</v>
+        <v>6920117</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16537,7 +16537,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>89631084</v>
+        <v>89631082</v>
       </c>
       <c r="B158" t="n">
         <v>80432</v>
@@ -16572,10 +16572,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>481524</v>
+        <v>481498</v>
       </c>
       <c r="R158" t="n">
-        <v>6920016</v>
+        <v>6920013</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16638,7 +16638,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>89631085</v>
+        <v>89631084</v>
       </c>
       <c r="B159" t="n">
         <v>80432</v>
@@ -16673,10 +16673,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>481600</v>
+        <v>481524</v>
       </c>
       <c r="R159" t="n">
-        <v>6919851</v>
+        <v>6920016</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -19264,51 +19264,49 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>117579652</v>
+        <v>96146709</v>
       </c>
       <c r="B185" t="n">
-        <v>78993</v>
+        <v>93213</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>353</v>
+        <v>2059</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
-      <c r="J185" t="inlineStr"/>
       <c r="K185" t="inlineStr"/>
-      <c r="N185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
           <t>Horten, Jmt</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>482237</v>
+        <v>482200</v>
       </c>
       <c r="R185" t="n">
-        <v>6918837</v>
+        <v>6918712</v>
       </c>
       <c r="S185" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T185" t="inlineStr">
         <is>
@@ -19332,12 +19330,22 @@
       </c>
       <c r="Y185" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2021-09-17</t>
+        </is>
+      </c>
+      <c r="Z185" t="inlineStr">
+        <is>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2021-09-17</t>
+        </is>
+      </c>
+      <c r="AB185" t="inlineStr">
+        <is>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -19346,26 +19354,25 @@
       <c r="AE185" t="b">
         <v>0</v>
       </c>
-      <c r="AF185" t="inlineStr"/>
       <c r="AG185" t="b">
         <v>0</v>
       </c>
       <c r="AT185" t="inlineStr"/>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>Marielle Löthman , Sebastian Kirppu</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>96146709</v>
+        <v>96146776</v>
       </c>
       <c r="B186" t="n">
         <v>93213</v>
@@ -19401,10 +19408,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>482200</v>
+        <v>482084</v>
       </c>
       <c r="R186" t="n">
-        <v>6918712</v>
+        <v>6918654</v>
       </c>
       <c r="S186" t="n">
         <v>25</v>
@@ -19436,7 +19443,7 @@
       </c>
       <c r="Z186" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
@@ -19446,7 +19453,7 @@
       </c>
       <c r="AB186" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -19473,49 +19480,51 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>96146776</v>
+        <v>117579644</v>
       </c>
       <c r="B187" t="n">
-        <v>93213</v>
+        <v>93197</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
+      <c r="J187" t="inlineStr"/>
       <c r="K187" t="inlineStr"/>
+      <c r="N187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
           <t>Horten, Jmt</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>482084</v>
+        <v>482260</v>
       </c>
       <c r="R187" t="n">
-        <v>6918654</v>
+        <v>6918704</v>
       </c>
       <c r="S187" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T187" t="inlineStr">
         <is>
@@ -19539,22 +19548,12 @@
       </c>
       <c r="Y187" t="inlineStr">
         <is>
-          <t>2021-09-17</t>
-        </is>
-      </c>
-      <c r="Z187" t="inlineStr">
-        <is>
-          <t>14:07</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
         <is>
-          <t>2021-09-17</t>
-        </is>
-      </c>
-      <c r="AB187" t="inlineStr">
-        <is>
-          <t>14:07</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -19563,28 +19562,29 @@
       <c r="AE187" t="b">
         <v>0</v>
       </c>
+      <c r="AF187" t="inlineStr"/>
       <c r="AG187" t="b">
         <v>0</v>
       </c>
       <c r="AT187" t="inlineStr"/>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Marielle Löthman , Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>117579697</v>
+        <v>117579645</v>
       </c>
       <c r="B188" t="n">
-        <v>91962</v>
+        <v>93197</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -19592,21 +19592,21 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -19619,10 +19619,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>482321</v>
+        <v>482353</v>
       </c>
       <c r="R188" t="n">
-        <v>6918867</v>
+        <v>6918745</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -19682,10 +19682,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>117579655</v>
+        <v>117579646</v>
       </c>
       <c r="B189" t="n">
-        <v>91831</v>
+        <v>93197</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -19693,21 +19693,21 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>3242</v>
+        <v>4364</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -19720,10 +19720,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>482226</v>
+        <v>482363</v>
       </c>
       <c r="R189" t="n">
-        <v>6918856</v>
+        <v>6918799</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -19783,7 +19783,7 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>117579644</v>
+        <v>117579650</v>
       </c>
       <c r="B190" t="n">
         <v>93197</v>
@@ -19821,10 +19821,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>482260</v>
+        <v>482235</v>
       </c>
       <c r="R190" t="n">
-        <v>6918704</v>
+        <v>6918743</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -19884,32 +19884,32 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>117579645</v>
+        <v>117579838</v>
       </c>
       <c r="B191" t="n">
-        <v>93197</v>
+        <v>79327</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -19922,10 +19922,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>482353</v>
+        <v>482193</v>
       </c>
       <c r="R191" t="n">
-        <v>6918745</v>
+        <v>6918714</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -19985,10 +19985,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>117579646</v>
+        <v>117579915</v>
       </c>
       <c r="B192" t="n">
-        <v>93197</v>
+        <v>79084</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -19996,21 +19996,21 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -20023,10 +20023,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>482363</v>
+        <v>482356</v>
       </c>
       <c r="R192" t="n">
-        <v>6918799</v>
+        <v>6918816</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -20086,10 +20086,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>117579650</v>
+        <v>117579703</v>
       </c>
       <c r="B193" t="n">
-        <v>93197</v>
+        <v>79946</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -20097,21 +20097,21 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -20124,10 +20124,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>482235</v>
+        <v>482319</v>
       </c>
       <c r="R193" t="n">
-        <v>6918743</v>
+        <v>6918649</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -20187,32 +20187,32 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>117579880</v>
+        <v>117579705</v>
       </c>
       <c r="B194" t="n">
-        <v>91872</v>
+        <v>79946</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -20225,10 +20225,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>482357</v>
+        <v>482242</v>
       </c>
       <c r="R194" t="n">
-        <v>6918836</v>
+        <v>6918749</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -20288,37 +20288,42 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>117579838</v>
+        <v>117579889</v>
       </c>
       <c r="B195" t="n">
-        <v>79327</v>
+        <v>57141</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
-      <c r="J195" t="inlineStr"/>
       <c r="K195" t="inlineStr"/>
+      <c r="L195" t="inlineStr"/>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
@@ -20326,10 +20331,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>482193</v>
+        <v>482358</v>
       </c>
       <c r="R195" t="n">
-        <v>6918714</v>
+        <v>6918807</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20370,7 +20375,6 @@
       <c r="AE195" t="b">
         <v>0</v>
       </c>
-      <c r="AF195" t="inlineStr"/>
       <c r="AG195" t="b">
         <v>0</v>
       </c>
@@ -20389,10 +20393,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>117579915</v>
+        <v>117579619</v>
       </c>
       <c r="B196" t="n">
-        <v>79084</v>
+        <v>79085</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -20400,21 +20404,21 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -20427,10 +20431,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>482356</v>
+        <v>482087</v>
       </c>
       <c r="R196" t="n">
-        <v>6918816</v>
+        <v>6918779</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20490,10 +20494,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>117579703</v>
+        <v>117579813</v>
       </c>
       <c r="B197" t="n">
-        <v>79946</v>
+        <v>79359</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -20501,21 +20505,21 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -20528,10 +20532,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>482319</v>
+        <v>482200</v>
       </c>
       <c r="R197" t="n">
-        <v>6918649</v>
+        <v>6918933</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -20591,10 +20595,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>117579705</v>
+        <v>117579652</v>
       </c>
       <c r="B198" t="n">
-        <v>79946</v>
+        <v>78993</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -20602,21 +20606,21 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
@@ -20629,10 +20633,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>482242</v>
+        <v>482237</v>
       </c>
       <c r="R198" t="n">
-        <v>6918749</v>
+        <v>6918837</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -20692,42 +20696,37 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>117579889</v>
+        <v>117579661</v>
       </c>
       <c r="B199" t="n">
-        <v>57141</v>
+        <v>92083</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>100138</v>
+        <v>1503</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
+      <c r="J199" t="inlineStr"/>
       <c r="K199" t="inlineStr"/>
-      <c r="L199" t="inlineStr"/>
-      <c r="M199" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
@@ -20735,10 +20734,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>482358</v>
+        <v>482261</v>
       </c>
       <c r="R199" t="n">
-        <v>6918807</v>
+        <v>6918909</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -20779,6 +20778,7 @@
       <c r="AE199" t="b">
         <v>0</v>
       </c>
+      <c r="AF199" t="inlineStr"/>
       <c r="AG199" t="b">
         <v>0</v>
       </c>
@@ -20797,10 +20797,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>117579619</v>
+        <v>117579697</v>
       </c>
       <c r="B200" t="n">
-        <v>79085</v>
+        <v>91962</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -20808,21 +20808,21 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>228912</v>
+        <v>2079</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -20835,10 +20835,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>482087</v>
+        <v>482321</v>
       </c>
       <c r="R200" t="n">
-        <v>6918779</v>
+        <v>6918867</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -20898,10 +20898,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>117579813</v>
+        <v>117579701</v>
       </c>
       <c r="B201" t="n">
-        <v>79359</v>
+        <v>91962</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -20909,21 +20909,21 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>185</v>
+        <v>2079</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -20936,10 +20936,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>482200</v>
+        <v>482297</v>
       </c>
       <c r="R201" t="n">
-        <v>6918933</v>
+        <v>6918898</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -20999,32 +20999,32 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>117579661</v>
+        <v>117579655</v>
       </c>
       <c r="B202" t="n">
-        <v>92083</v>
+        <v>91831</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>1503</v>
+        <v>3242</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -21037,10 +21037,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>482261</v>
+        <v>482226</v>
       </c>
       <c r="R202" t="n">
-        <v>6918909</v>
+        <v>6918856</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -21100,10 +21100,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>117579701</v>
+        <v>117579955</v>
       </c>
       <c r="B203" t="n">
-        <v>91962</v>
+        <v>93197</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -21111,21 +21111,21 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
@@ -21138,10 +21138,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>482297</v>
+        <v>482213</v>
       </c>
       <c r="R203" t="n">
-        <v>6918898</v>
+        <v>6918907</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -21201,7 +21201,7 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>117579955</v>
+        <v>117579967</v>
       </c>
       <c r="B204" t="n">
         <v>93197</v>
@@ -21239,10 +21239,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>482213</v>
+        <v>482221</v>
       </c>
       <c r="R204" t="n">
-        <v>6918907</v>
+        <v>6918905</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -21302,32 +21302,32 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>117579967</v>
+        <v>117579880</v>
       </c>
       <c r="B205" t="n">
-        <v>93197</v>
+        <v>91872</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
@@ -21340,10 +21340,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>482221</v>
+        <v>482357</v>
       </c>
       <c r="R205" t="n">
-        <v>6918905</v>
+        <v>6918836</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
